--- a/artfynd/A 37482-2020 artfynd.xlsx
+++ b/artfynd/A 37482-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126545795</v>
+        <v>126545798</v>
       </c>
       <c r="B2" t="n">
-        <v>44801</v>
+        <v>44806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102018</v>
+        <v>102021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -786,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126545798</v>
+        <v>126545795</v>
       </c>
       <c r="B3" t="n">
-        <v>44806</v>
+        <v>44801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,26 +789,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102021</v>
+        <v>102018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
